--- a/Homomorphic Encription/resultados/resultados.xlsx
+++ b/Homomorphic Encription/resultados/resultados.xlsx
@@ -1388,7 +1388,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -1620,21 +1620,42 @@
       <c r="B5" s="3" t="n">
         <v>98.2456</v>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>97.36839999999999</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.8772</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>98.0956</v>
       </c>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>97.1583</v>
+      </c>
       <c r="G5" s="4" t="n">
         <v>0.0012</v>
       </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="H5" s="4" t="n">
+        <v>764.1934</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>651475.5111999999</v>
+      </c>
       <c r="J5" t="n">
         <v>97185.09269999999</v>
       </c>
-      <c r="L5" s="5" t="n"/>
+      <c r="K5" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1967,21 +1988,42 @@
       <c r="B13" s="3" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="C13" s="3" t="n">
+        <v>86.675</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0.225</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>58.2254</v>
       </c>
-      <c r="F13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>56.8803</v>
+      </c>
       <c r="G13" s="4" t="n">
         <v>0.0068</v>
       </c>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>2675.7941</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>393917.1639</v>
+      </c>
       <c r="J13" t="n">
         <v>588860.2015</v>
       </c>
-      <c r="L13" s="5" t="n"/>
+      <c r="K13" t="n">
+        <v>1.4949</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1994,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,7 +2379,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>BreastCancer_Full30  ·  plana  ·  accuracy 98.25%  (pred #13)</t>
+          <t>BreastCancer_Full30  ·  homomorfica  ·  accuracy 97.37%  (pred #124)</t>
         </is>
       </c>
     </row>
@@ -2370,10 +2412,10 @@
         </is>
       </c>
       <c r="C41" s="10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2392,7 +2434,7 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Credit_PCA5  ·  homomorfica  ·  accuracy 81.16%  (pred #116)</t>
+          <t>BreastCancer_Full30  ·  homomorfica  ·  accuracy 97.37%  (pred #125)</t>
         </is>
       </c>
     </row>
@@ -2425,10 +2467,10 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2438,16 +2480,16 @@
         </is>
       </c>
       <c r="C48" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Credit_PCA5  ·  plana  ·  accuracy 81.16%  (pred #20)</t>
+          <t>BreastCancer_Full30  ·  plana  ·  accuracy 98.25%  (pred #13)</t>
         </is>
       </c>
     </row>
@@ -2480,10 +2522,10 @@
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="D53" s="11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2493,16 +2535,16 @@
         </is>
       </c>
       <c r="C54" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Obesity_16-7  ·  homomorfica  ·  accuracy 73.76%  (pred #117)</t>
+          <t>Credit_PCA5  ·  homomorfica  ·  accuracy 81.16%  (pred #116)</t>
         </is>
       </c>
     </row>
@@ -2514,37 +2556,12 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Clase 0</t>
+          <t>Negativo</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Clase 1</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>Clase 2</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
-        <is>
-          <t>Clase 3</t>
-        </is>
-      </c>
-      <c r="G58" s="8" t="inlineStr">
-        <is>
-          <t>Clase 4</t>
-        </is>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>Clase 5</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Clase 6</t>
+          <t>Positivo</t>
         </is>
       </c>
     </row>
@@ -2556,295 +2573,152 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 0</t>
+          <t>Real Negativo</t>
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 1</t>
+          <t>Real Positivo</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="11" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Credit_PCA5  ·  plana  ·  accuracy 81.16%  (pred #20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Real Negativo</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Real Positivo</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-7  ·  homomorfica  ·  accuracy 73.76%  (pred #117)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 3</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 4</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 5</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Clase 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 0</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="G60" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 2</t>
-        </is>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="F61" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 3</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="G62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 4</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="H63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 5</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="I64" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 6</t>
-        </is>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I65" s="10" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_16-7  ·  plana  ·  accuracy 73.76%  (pred #22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Predicho →</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 0</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 1</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 2</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 3</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 4</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 5</t>
-        </is>
-      </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>Clase 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>Real ↓</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 0</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="D70" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="D71" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>0</v>
@@ -2853,72 +2727,72 @@
         <v>0</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="F72" s="11" t="n">
-        <v>10</v>
       </c>
       <c r="G72" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" s="10" t="n">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="G73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
@@ -2928,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="E74" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="G74" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F74" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H74" s="11" t="n">
         <v>0</v>
@@ -2946,152 +2820,152 @@
     <row r="75">
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H75" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="11" t="n">
+      <c r="I75" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H75" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="I75" s="11" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G76" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H76" s="11" t="n">
+      <c r="H76" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="I76" s="10" t="n">
+      <c r="I77" s="10" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_16-10-7  ·  homomorfica  ·  accuracy 92.20%  (pred #118)</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
-      <c r="B80" s="7" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-7  ·  plana  ·  accuracy 73.76%  (pred #22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C81" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="D81" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D82" s="10" t="n">
-        <v>48</v>
+      <c r="C82" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="E82" s="11" t="n">
         <v>0</v>
@@ -3103,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I82" s="11" t="n">
         <v>0</v>
@@ -3112,63 +2986,63 @@
     <row r="83">
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D83" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="D83" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="F83" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="G83" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="G84" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
@@ -3178,13 +3052,13 @@
         <v>0</v>
       </c>
       <c r="E85" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="G85" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F85" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H85" s="11" t="n">
         <v>0</v>
@@ -3196,42 +3070,42 @@
     <row r="86">
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H86" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="11" t="n">
+      <c r="I86" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H86" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I86" s="11" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>3</v>
@@ -3242,106 +3116,106 @@
       <c r="G87" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="I87" s="10" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_16-10-7  ·  plana  ·  accuracy 92.43%  (pred #24)</t>
-        </is>
+      <c r="H87" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="7" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-10-7  ·  homomorfica  ·  accuracy 92.20%  (pred #118)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D92" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F92" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr">
+      <c r="G92" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C92" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="D92" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E92" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C93" s="11" t="n">
+      <c r="C93" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D93" s="11" t="n">
         <v>3</v>
-      </c>
-      <c r="D93" s="10" t="n">
-        <v>48</v>
       </c>
       <c r="E93" s="11" t="n">
         <v>0</v>
@@ -3353,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I93" s="11" t="n">
         <v>0</v>
@@ -3362,26 +3236,26 @@
     <row r="94">
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E94" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D94" s="11" t="n">
+      <c r="F94" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="F94" s="11" t="n">
-        <v>3</v>
       </c>
       <c r="G94" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I94" s="11" t="n">
         <v>0</v>
@@ -3390,7 +3264,7 @@
     <row r="95">
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
@@ -3399,11 +3273,11 @@
       <c r="D95" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F95" s="10" t="n">
-        <v>58</v>
+      <c r="E95" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="G95" s="11" t="n">
         <v>0</v>
@@ -3412,13 +3286,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
@@ -3428,13 +3302,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="G96" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F96" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H96" s="11" t="n">
         <v>0</v>
@@ -3446,45 +3320,45 @@
     <row r="97">
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H97" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="11" t="n">
+      <c r="I97" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H97" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="I97" s="11" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="E98" s="11" t="n">
-        <v>3</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0</v>
@@ -3492,106 +3366,106 @@
       <c r="G98" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H98" s="11" t="n">
+      <c r="H98" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="I98" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="I98" s="10" t="n">
+    </row>
+    <row r="99">
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I99" s="10" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_16-10-7_rg  ·  homomorfica  ·  accuracy 90.31%  (pred #119)</t>
-        </is>
-      </c>
-    </row>
     <row r="102">
-      <c r="B102" s="7" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-10-7  ·  plana  ·  accuracy 92.43%  (pred #24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D103" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
+      <c r="F103" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G102" s="8" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C103" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="D103" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E103" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C104" s="11" t="n">
+      <c r="C104" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D104" s="11" t="n">
         <v>2</v>
-      </c>
-      <c r="D104" s="10" t="n">
-        <v>46</v>
       </c>
       <c r="E104" s="11" t="n">
         <v>0</v>
@@ -3603,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I104" s="11" t="n">
         <v>0</v>
@@ -3612,35 +3486,35 @@
     <row r="105">
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E105" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="F105" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="F105" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="G105" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I105" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="I105" s="11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
@@ -3649,17 +3523,17 @@
       <c r="D106" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E106" s="11" t="n">
+      <c r="E106" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="F106" s="11" t="n">
         <v>3</v>
-      </c>
-      <c r="F106" s="10" t="n">
-        <v>56</v>
       </c>
       <c r="G106" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="11" t="n">
         <v>0</v>
@@ -3668,7 +3542,7 @@
     <row r="107">
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
@@ -3678,13 +3552,13 @@
         <v>0</v>
       </c>
       <c r="E107" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="G107" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F107" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H107" s="11" t="n">
         <v>0</v>
@@ -3696,42 +3570,42 @@
     <row r="108">
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E108" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H108" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="11" t="n">
+      <c r="I108" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H108" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I108" s="11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E109" s="11" t="n">
         <v>0</v>
@@ -3742,106 +3616,106 @@
       <c r="G109" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="11" t="n">
+      <c r="H109" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="I109" s="10" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_16-10-7_rg  ·  plana  ·  accuracy 93.14%  (pred #34)</t>
-        </is>
+      <c r="I110" s="10" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="7" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-10-7_rg  ·  homomorfica  ·  accuracy 90.31%  (pred #119)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C114" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="D114" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E114" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D115" s="10" t="n">
-        <v>48</v>
+      <c r="C115" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="E115" s="11" t="n">
         <v>0</v>
@@ -3853,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I115" s="11" t="n">
         <v>0</v>
@@ -3862,26 +3736,26 @@
     <row r="116">
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E116" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="11" t="n">
+      <c r="F116" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="F116" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="G116" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I116" s="11" t="n">
         <v>0</v>
@@ -3890,7 +3764,7 @@
     <row r="117">
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
@@ -3899,11 +3773,11 @@
       <c r="D117" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="11" t="n">
+      <c r="E117" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="F117" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="F117" s="10" t="n">
-        <v>59</v>
       </c>
       <c r="G117" s="11" t="n">
         <v>0</v>
@@ -3912,13 +3786,13 @@
         <v>0</v>
       </c>
       <c r="I117" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
@@ -3928,16 +3802,16 @@
         <v>0</v>
       </c>
       <c r="E118" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="G118" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="11" t="n">
+      <c r="H118" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="G118" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="H118" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="I118" s="11" t="n">
         <v>0</v>
@@ -3946,45 +3820,45 @@
     <row r="119">
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E119" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H119" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="11" t="n">
+      <c r="I119" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H119" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="I119" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D120" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="E120" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="F120" s="11" t="n">
         <v>0</v>
@@ -3992,109 +3866,109 @@
       <c r="G120" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I120" s="10" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_12-7_rg  ·  homomorfica  ·  accuracy 63.83%  (pred #120)</t>
-        </is>
+      <c r="H120" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I120" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I121" s="10" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="7" t="inlineStr">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_16-10-7_rg  ·  plana  ·  accuracy 93.14%  (pred #34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
+      <c r="E125" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
+      <c r="F125" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G124" s="8" t="inlineStr">
+      <c r="G125" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C125" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="D125" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E125" s="11" t="n">
+      <c r="C126" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F125" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I125" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="D126" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E126" s="11" t="n">
-        <v>4</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -4103,44 +3977,44 @@
         <v>0</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I126" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D127" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="D127" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G127" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H127" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="I127" s="11" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
@@ -4149,11 +4023,11 @@
       <c r="D128" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="11" t="n">
+      <c r="E128" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="F128" s="11" t="n">
         <v>1</v>
-      </c>
-      <c r="F128" s="10" t="n">
-        <v>59</v>
       </c>
       <c r="G128" s="11" t="n">
         <v>0</v>
@@ -4168,7 +4042,7 @@
     <row r="129">
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
@@ -4178,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="E129" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="G129" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F129" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H129" s="11" t="n">
         <v>0</v>
@@ -4196,155 +4070,155 @@
     <row r="130">
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G130" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H130" s="10" t="n">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H130" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I130" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="9" t="inlineStr">
         <is>
+          <t>Real Clase 5</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="I131" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="9" t="inlineStr">
+        <is>
           <t>Real Clase 6</t>
         </is>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D131" s="11" t="n">
+      <c r="C132" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="F131" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="G131" s="11" t="n">
+      <c r="D132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H131" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="I131" s="10" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_12-7_rg  ·  plana  ·  accuracy 63.83%  (pred #44)</t>
-        </is>
+      <c r="F132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I132" s="10" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="7" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_12-7_rg  ·  homomorfica  ·  accuracy 63.83%  (pred #120)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D135" s="8" t="inlineStr">
+      <c r="D136" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E135" s="8" t="inlineStr">
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F135" s="8" t="inlineStr">
+      <c r="F136" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G135" s="8" t="inlineStr">
+      <c r="G136" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H135" s="8" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="I136" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B136" s="9" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C136" s="10" t="n">
+      <c r="C137" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="D136" s="11" t="n">
+      <c r="D137" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E136" s="11" t="n">
+      <c r="E137" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F136" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I136" s="11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C137" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="D137" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E137" s="11" t="n">
-        <v>4</v>
       </c>
       <c r="F137" s="11" t="n">
         <v>0</v>
@@ -4353,57 +4227,57 @@
         <v>0</v>
       </c>
       <c r="H137" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I137" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>49</v>
+        <v>19</v>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G138" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I138" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C139" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="10" t="n">
-        <v>59</v>
+        <v>2</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="G139" s="11" t="n">
         <v>0</v>
@@ -4412,13 +4286,13 @@
         <v>0</v>
       </c>
       <c r="I139" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C140" s="11" t="n">
@@ -4428,13 +4302,13 @@
         <v>0</v>
       </c>
       <c r="E140" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="G140" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F140" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H140" s="11" t="n">
         <v>0</v>
@@ -4446,214 +4320,214 @@
     <row r="141">
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C141" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G141" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H141" s="10" t="n">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H141" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I141" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="9" t="inlineStr">
         <is>
+          <t>Real Clase 5</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G142" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="9" t="inlineStr">
+        <is>
           <t>Real Clase 6</t>
         </is>
       </c>
-      <c r="C142" s="11" t="n">
+      <c r="C143" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="D142" s="11" t="n">
+      <c r="D143" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="11" t="n">
+      <c r="E143" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="F142" s="11" t="n">
+      <c r="F143" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G142" s="11" t="n">
+      <c r="G143" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H142" s="11" t="n">
+      <c r="H143" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="I142" s="10" t="n">
+      <c r="I143" s="10" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_12-5-7_rg  ·  homomorfica  ·  accuracy 64.78%  (pred #121)</t>
-        </is>
-      </c>
-    </row>
     <row r="146">
-      <c r="B146" s="7" t="inlineStr">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_12-7_rg  ·  plana  ·  accuracy 63.83%  (pred #44)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr">
+      <c r="C147" s="8" t="inlineStr">
         <is>
           <t>Clase 0</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr">
+      <c r="D147" s="8" t="inlineStr">
         <is>
           <t>Clase 1</t>
         </is>
       </c>
-      <c r="E146" s="8" t="inlineStr">
+      <c r="E147" s="8" t="inlineStr">
         <is>
           <t>Clase 2</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
+      <c r="F147" s="8" t="inlineStr">
         <is>
           <t>Clase 3</t>
         </is>
       </c>
-      <c r="G146" s="8" t="inlineStr">
+      <c r="G147" s="8" t="inlineStr">
         <is>
           <t>Clase 4</t>
         </is>
       </c>
-      <c r="H146" s="8" t="inlineStr">
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>Clase 5</t>
         </is>
       </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="I147" s="8" t="inlineStr">
         <is>
           <t>Clase 6</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="7" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B148" s="9" t="inlineStr">
         <is>
           <t>Real Clase 0</t>
         </is>
       </c>
-      <c r="C147" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="D147" s="11" t="n">
+      <c r="C148" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D148" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="E147" s="11" t="n">
+      <c r="E148" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F147" s="11" t="n">
+      <c r="F148" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="G147" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I147" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C148" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D148" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="E148" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F148" s="11" t="n">
-        <v>1</v>
       </c>
       <c r="G148" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I148" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C149" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D149" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>51</v>
+        <v>19</v>
+      </c>
+      <c r="D149" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G149" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H149" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I149" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C150" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F150" s="10" t="n">
-        <v>51</v>
+        <v>2</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>11</v>
       </c>
       <c r="G150" s="11" t="n">
         <v>0</v>
@@ -4662,13 +4536,13 @@
         <v>0</v>
       </c>
       <c r="I150" s="11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C151" s="11" t="n">
@@ -4680,11 +4554,11 @@
       <c r="E151" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F151" s="11" t="n">
+      <c r="F151" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="G151" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="G151" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H151" s="11" t="n">
         <v>0</v>
@@ -4696,229 +4570,229 @@
     <row r="152">
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C152" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D152" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H152" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G152" s="11" t="n">
+      <c r="I152" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="H152" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I152" s="11" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="9" t="inlineStr">
         <is>
+          <t>Real Clase 5</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D153" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="9" t="inlineStr">
+        <is>
           <t>Real Clase 6</t>
         </is>
       </c>
-      <c r="C153" s="11" t="n">
+      <c r="C154" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D154" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G154" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D153" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E153" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="F153" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G153" s="11" t="n">
+      <c r="I154" s="10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_12-5-7_rg  ·  homomorfica  ·  accuracy 64.78%  (pred #121)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="F158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 3</t>
+        </is>
+      </c>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 4</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 5</t>
+        </is>
+      </c>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>Clase 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B159" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 0</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="D159" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E159" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H153" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I153" s="10" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>Obesity_12-5-7_rg  ·  plana  ·  accuracy 69.98%  (pred #46)</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>Predicho →</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 0</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 1</t>
-        </is>
-      </c>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 2</t>
-        </is>
-      </c>
-      <c r="F157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 3</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 4</t>
-        </is>
-      </c>
-      <c r="H157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 5</t>
-        </is>
-      </c>
-      <c r="I157" s="8" t="inlineStr">
-        <is>
-          <t>Clase 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>Real ↓</t>
-        </is>
-      </c>
-      <c r="B158" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 0</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="D158" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E158" s="11" t="n">
+      <c r="F159" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="F158" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I158" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="9" t="inlineStr">
-        <is>
-          <t>Real Clase 1</t>
-        </is>
-      </c>
-      <c r="C159" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="D159" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="E159" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F159" s="11" t="n">
-        <v>2</v>
       </c>
       <c r="G159" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H159" s="11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I159" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 2</t>
+          <t>Real Clase 1</t>
         </is>
       </c>
       <c r="C160" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D160" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="F160" s="11" t="n">
-        <v>8</v>
-      </c>
       <c r="G160" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" s="11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I160" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 3</t>
+          <t>Real Clase 2</t>
         </is>
       </c>
       <c r="C161" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D161" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F161" s="10" t="n">
-        <v>58</v>
+      <c r="E161" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>3</v>
       </c>
       <c r="G161" s="11" t="n">
         <v>0</v>
       </c>
       <c r="H161" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I161" s="11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 4</t>
+          <t>Real Clase 3</t>
         </is>
       </c>
       <c r="C162" s="11" t="n">
@@ -4928,191 +4802,359 @@
         <v>0</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="G162" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="G162" s="10" t="n">
-        <v>64</v>
       </c>
       <c r="H162" s="11" t="n">
         <v>0</v>
       </c>
       <c r="I162" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 5</t>
+          <t>Real Clase 4</t>
         </is>
       </c>
       <c r="C163" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D163" s="11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E163" s="11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F163" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G163" s="11" t="n">
+      <c r="G163" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H163" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H163" s="10" t="n">
-        <v>29</v>
-      </c>
       <c r="I163" s="11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>Real Clase 6</t>
+          <t>Real Clase 5</t>
         </is>
       </c>
       <c r="C164" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D164" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G164" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H164" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="I164" s="10" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>Diabetes_PCA5  ·  homomorfica  ·  accuracy 86.22%  (pred #122)</t>
-        </is>
+      <c r="H164" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I164" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 6</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I165" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="168">
-      <c r="B168" s="7" t="inlineStr">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>Obesity_12-5-7_rg  ·  plana  ·  accuracy 69.98%  (pred #46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="7" t="inlineStr">
         <is>
           <t>Predicho →</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 0</t>
+        </is>
+      </c>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 1</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 2</t>
+        </is>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 3</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 4</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 5</t>
+        </is>
+      </c>
+      <c r="I169" s="8" t="inlineStr">
+        <is>
+          <t>Clase 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
         <is>
           <t>Real ↓</t>
         </is>
       </c>
-      <c r="B169" s="9" t="inlineStr">
-        <is>
-          <t>Real Negativo</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="n">
-        <v>3378</v>
-      </c>
-      <c r="D169" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="170">
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>Real Positivo</t>
-        </is>
-      </c>
-      <c r="C170" s="11" t="n">
-        <v>486</v>
-      </c>
-      <c r="D170" s="10" t="n">
-        <v>71</v>
+          <t>Real Clase 0</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 1</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D171" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I171" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 2</t>
+        </is>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G172" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" s="11" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>Diabetes_PCA5  ·  plana  ·  accuracy 86.22%  (pred #56)</t>
-        </is>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 3</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="G173" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>Predicho →</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t>Negativo</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="inlineStr">
-        <is>
-          <t>Positivo</t>
-        </is>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>Real Clase 4</t>
+        </is>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="H174" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t>Real ↓</t>
-        </is>
-      </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>Real Negativo</t>
-        </is>
-      </c>
-      <c r="C175" s="10" t="n">
-        <v>3378</v>
+          <t>Real Clase 5</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="n">
+        <v>4</v>
       </c>
       <c r="D175" s="11" t="n">
-        <v>65</v>
+        <v>5</v>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="I175" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>Real Positivo</t>
+          <t>Real Clase 6</t>
         </is>
       </c>
       <c r="C176" s="11" t="n">
-        <v>486</v>
-      </c>
-      <c r="D176" s="10" t="n">
-        <v>71</v>
+        <v>7</v>
+      </c>
+      <c r="D176" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G176" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I176" s="10" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>Diabetes_12-5  ·  plana  ·  accuracy 86.90%  (pred #58)</t>
+          <t>Diabetes_PCA5  ·  homomorfica  ·  accuracy 86.22%  (pred #122)</t>
         </is>
       </c>
     </row>
@@ -5145,10 +5187,10 @@
         </is>
       </c>
       <c r="C181" s="10" t="n">
-        <v>3395</v>
+        <v>3378</v>
       </c>
       <c r="D181" s="11" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="182">
@@ -5158,9 +5200,174 @@
         </is>
       </c>
       <c r="C182" s="11" t="n">
+        <v>486</v>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Diabetes_PCA5  ·  plana  ·  accuracy 86.22%  (pred #56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>Real Negativo</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="n">
+        <v>3378</v>
+      </c>
+      <c r="D187" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="9" t="inlineStr">
+        <is>
+          <t>Real Positivo</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>486</v>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>Diabetes_12-5  ·  homomorfica  ·  accuracy 86.67%  (pred #123)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>Real Negativo</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="n">
+        <v>3396</v>
+      </c>
+      <c r="D193" s="11" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>Real Positivo</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>486</v>
+      </c>
+      <c r="D194" s="10" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>Diabetes_12-5  ·  plana  ·  accuracy 86.90%  (pred #58)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>Predicho →</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Negativo</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>Real ↓</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>Real Negativo</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="n">
+        <v>3395</v>
+      </c>
+      <c r="D199" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>Real Positivo</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="n">
         <v>476</v>
       </c>
-      <c r="D182" s="10" t="n">
+      <c r="D200" s="10" t="n">
         <v>81</v>
       </c>
     </row>
@@ -5255,7 +5462,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C59:I65">
+  <conditionalFormatting sqref="C59:D60">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5265,7 +5472,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70:I76">
+  <conditionalFormatting sqref="C65:D66">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -5275,7 +5482,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C81:I87">
+  <conditionalFormatting sqref="C71:I77">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -5285,7 +5492,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C92:I98">
+  <conditionalFormatting sqref="C82:I88">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -5295,7 +5502,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C103:I109">
+  <conditionalFormatting sqref="C93:I99">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -5305,7 +5512,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C114:I120">
+  <conditionalFormatting sqref="C104:I110">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -5315,7 +5522,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C125:I131">
+  <conditionalFormatting sqref="C115:I121">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5325,7 +5532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C136:I142">
+  <conditionalFormatting sqref="C126:I132">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -5335,7 +5542,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C147:I153">
+  <conditionalFormatting sqref="C137:I143">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -5345,7 +5552,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C158:I164">
+  <conditionalFormatting sqref="C148:I154">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5355,7 +5562,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C169:D170">
+  <conditionalFormatting sqref="C159:I165">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
@@ -5365,7 +5572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C175:D176">
+  <conditionalFormatting sqref="C170:I176">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
@@ -5385,6 +5592,36 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C187:D188">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C193:D194">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C199:D200">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="004472C4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5395,7 +5632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN23"/>
+  <dimension ref="A1:BN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5433,7 +5670,7 @@
     <col width="23" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
     <col width="21" customWidth="1" min="35" max="35"/>
-    <col width="30" customWidth="1" min="36" max="36"/>
+    <col width="40" customWidth="1" min="36" max="36"/>
     <col width="19" customWidth="1" min="37" max="37"/>
     <col width="14" customWidth="1" min="38" max="38"/>
     <col width="40" customWidth="1" min="39" max="39"/>
@@ -9658,6 +9895,627 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CDC Diabetes Health Indicators</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Diabetes_12-5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>12 -&gt; 5 -&gt; 2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-13 20:11:22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>86.675</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>55.6909</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>13.325</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>56.8803</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>86.675</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>82.74120000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>73.82510000000001</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>55.6909</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>12.7469</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>98.6349</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>60.1695</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>87.4807</v>
+      </c>
+      <c r="V24" s="3" t="n"/>
+      <c r="W24" s="5" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Y24" s="5" t="n"/>
+      <c r="Z24" t="n">
+        <v>3467</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>533</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3396</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>486</v>
+      </c>
+      <c r="AF24" s="4" t="n">
+        <v>2675.7941</v>
+      </c>
+      <c r="AG24" s="4" t="n">
+        <v>668.9485</v>
+      </c>
+      <c r="AH24" s="4" t="n">
+        <v>1.4949</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>16384</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>[60, 50, 50, 50, 50, 50, 60]</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>[-8.084490776062012, 8.97476577758789]</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>[0.3570829869920937, 0.5182422783752447, 0.1383272759973112, -0.002810298007871312, -0.002446244231959789, 0.00010267826761588137, 1.854704783605354e-05, -1.0340486852193337e-06]</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS24" s="4" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="AT24" s="4" t="n"/>
+      <c r="AU24" s="4" t="n"/>
+      <c r="AV24" s="4" t="n"/>
+      <c r="AW24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA24" s="4" t="n">
+        <v>15160.84</v>
+      </c>
+      <c r="BB24" s="4" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="BC24" s="4" t="n">
+        <v>15245.93</v>
+      </c>
+      <c r="BD24" s="5" t="n">
+        <v>0.4748</v>
+      </c>
+      <c r="BE24" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="BF24" s="5" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="BG24" s="5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BH24" s="5" t="n">
+        <v>2.267</v>
+      </c>
+      <c r="BI24" s="5" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="BJ24" s="5" t="n">
+        <v>2.252</v>
+      </c>
+      <c r="BK24" s="5" t="n">
+        <v>7.013</v>
+      </c>
+      <c r="BL24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>[[3396, 47], [486, 71]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>124</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Breast Cancer Wisconsin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30 -&gt; 16 -&gt; 8 -&gt; 2</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-14 08:52:12</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>114</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>97.36839999999999</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>96.9246</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>2.6316</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>97.1583</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>97.36839999999999</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>97.3616</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>97.4106</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>96.9246</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>97.56100000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>97.2603</v>
+      </c>
+      <c r="V25" s="3" t="n"/>
+      <c r="W25" s="5" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="X25" s="5" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="Y25" s="5" t="n"/>
+      <c r="Z25" t="n">
+        <v>111</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" s="4" t="n">
+        <v>1534.3504</v>
+      </c>
+      <c r="AG25" s="4" t="n">
+        <v>13459.2137</v>
+      </c>
+      <c r="AH25" s="4" t="n">
+        <v>0.0743</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>32768</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>[60, 50, 50, 50, 50, 50, 50, 50, 50, 50, 60]</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>[-13.756940841674805, 27.039508819580078]</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>[0.8024540526472421, 0.5019022761549353, 0.061903297673690925, -0.00035096726522619565, -0.00022321316613287346, 3.938590877466105e-06, 3.4558160829059706e-07, -9.342649591474008e-09]</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" s="4" t="n">
+        <v>1.9128</v>
+      </c>
+      <c r="AT25" s="4" t="n"/>
+      <c r="AU25" s="4" t="n"/>
+      <c r="AV25" s="4" t="n"/>
+      <c r="AW25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>49</v>
+      </c>
+      <c r="BA25" s="4" t="n">
+        <v>7429.36</v>
+      </c>
+      <c r="BB25" s="4" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="BC25" s="4" t="n">
+        <v>7494.15</v>
+      </c>
+      <c r="BD25" s="5" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BE25" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="BF25" s="5" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="BG25" s="5" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="BH25" s="5" t="n">
+        <v>4.226</v>
+      </c>
+      <c r="BI25" s="5" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BJ25" s="5" t="n">
+        <v>4.156</v>
+      </c>
+      <c r="BK25" s="5" t="n">
+        <v>5.388</v>
+      </c>
+      <c r="BL25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>[[71, 1], [2, 40]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Breast Cancer Wisconsin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30 -&gt; 16 -&gt; 8 -&gt; 2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-14 09:33:13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>114</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>97.36839999999999</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>96.9246</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>2.6316</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>97.1583</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>97.36839999999999</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>97.3616</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>97.4106</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>96.9246</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>97.56100000000001</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>97.2603</v>
+      </c>
+      <c r="V26" s="3" t="n"/>
+      <c r="W26" s="5" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="Y26" s="5" t="n"/>
+      <c r="Z26" t="n">
+        <v>111</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="4" t="n">
+        <v>764.1934</v>
+      </c>
+      <c r="AG26" s="4" t="n">
+        <v>6703.451</v>
+      </c>
+      <c r="AH26" s="4" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>16384</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>[60, 35, 35, 35, 35, 35, 35, 35, 35, 35, 60]</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>[-13.756940841674805, 27.039508819580078]</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>[0.8024540526472421, 0.5019022761549353, 0.061903297673690925, -0.00035096726522619565, -0.00022321316613287346, 3.938590877466105e-06, 3.4558160829059706e-07, -9.342649591474008e-09]</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS26" s="4" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="n"/>
+      <c r="AV26" s="4" t="n"/>
+      <c r="AW26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA26" s="4" t="n">
+        <v>3628.93</v>
+      </c>
+      <c r="BB26" s="4" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="BC26" s="4" t="n">
+        <v>3653.87</v>
+      </c>
+      <c r="BD26" s="5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BE26" s="5" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="BF26" s="5" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="BG26" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BH26" s="5" t="n">
+        <v>2.493</v>
+      </c>
+      <c r="BI26" s="5" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BJ26" s="5" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="BK26" s="5" t="n">
+        <v>7.142</v>
+      </c>
+      <c r="BL26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>[[71, 1], [2, 40]]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9669,7 +10527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13406,6 +14264,240 @@
       </c>
       <c r="K95" t="n">
         <v>557</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>595</v>
+      </c>
+      <c r="B96" t="n">
+        <v>123</v>
+      </c>
+      <c r="C96" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Diabetes_12-5</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>87.4807</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>98.6349</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>92.7235</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>12.7469</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3443</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>596</v>
+      </c>
+      <c r="B97" t="n">
+        <v>123</v>
+      </c>
+      <c r="C97" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Diabetes_12-5</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>60.1695</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>12.7469</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>21.037</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>98.6349</v>
+      </c>
+      <c r="K97" t="n">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>597</v>
+      </c>
+      <c r="B98" t="n">
+        <v>124</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>97.2603</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>97.931</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="K98" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>598</v>
+      </c>
+      <c r="B99" t="n">
+        <v>124</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>97.56100000000001</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>96.38549999999999</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="K99" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>599</v>
+      </c>
+      <c r="B100" t="n">
+        <v>125</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>97.2603</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>97.931</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="K100" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>600</v>
+      </c>
+      <c r="B101" t="n">
+        <v>125</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BreastCancer_Full30</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>homomorfica</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>97.56100000000001</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>95.2381</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>96.38549999999999</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>98.61109999999999</v>
+      </c>
+      <c r="K101" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
